--- a/花境设计辅助系统/花境设计辅助工具_数据库.xlsx
+++ b/花境设计辅助系统/花境设计辅助工具_数据库.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\01工作\总工工作文件\01个人文件\编程专业检索工具\规范检索工具\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\work\工作室——设计文件（研究学习的重要资料）\01个人文件\Twolobster 2026\花境设计辅助系统\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2A5183-7367-4D77-8D2A-6C162B539807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2CE129-BA3F-45C8-830F-D05B1CB53497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="539">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2035,6 +2035,26 @@
   </si>
   <si>
     <t>绵毛水苏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柳叶星河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柳叶星河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80-200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f98</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2470,7 +2490,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J242"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="24.875" customWidth="1"/>
@@ -3040,27 +3060,43 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="B20" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -3070,10 +3106,11 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -3083,11 +3120,10 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -3097,11 +3133,11 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -3111,11 +3147,11 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -3125,11 +3161,11 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -3139,11 +3175,11 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -3153,11 +3189,11 @@
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -3167,11 +3203,11 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="2" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -3181,82 +3217,66 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>78</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>18</v>
@@ -3268,13 +3288,13 @@
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="3" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>78</v>
@@ -3283,25 +3303,25 @@
         <v>30</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>31</v>
@@ -3309,14 +3329,14 @@
       <c r="E35" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>244</v>
+      <c r="F35" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>18</v>
@@ -3328,10 +3348,10 @@
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>31</v>
@@ -3340,28 +3360,28 @@
         <v>78</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>31</v>
@@ -3370,28 +3390,28 @@
         <v>78</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="3" t="s">
-        <v>268</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>31</v>
@@ -3399,29 +3419,29 @@
       <c r="E38" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>246</v>
+      <c r="F38" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>254</v>
+        <v>117</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>271</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="3" t="s">
-        <v>408</v>
+        <v>268</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>409</v>
+        <v>266</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>31</v>
@@ -3429,29 +3449,29 @@
       <c r="E39" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>164</v>
+      <c r="F39" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>269</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>410</v>
+        <v>254</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="3" t="s">
-        <v>484</v>
+        <v>408</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>483</v>
+        <v>409</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>31</v>
@@ -3459,29 +3479,29 @@
       <c r="E40" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>30</v>
+      <c r="F40" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>485</v>
+        <v>410</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="3" t="s">
-        <v>358</v>
+        <v>484</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>31</v>
@@ -3490,13 +3510,13 @@
         <v>78</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>498</v>
+        <v>140</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>124</v>
+        <v>485</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>18</v>
@@ -3508,10 +3528,10 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>31</v>
@@ -3523,7 +3543,7 @@
         <v>246</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>124</v>
@@ -3537,23 +3557,39 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="B43" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -3567,7 +3603,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -3581,7 +3617,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -3595,7 +3631,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -3609,7 +3645,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -3623,7 +3659,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -3637,7 +3673,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -3648,146 +3684,130 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="3" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>86</v>
+      <c r="F54" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>31</v>
@@ -3796,28 +3816,28 @@
         <v>79</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>31</v>
@@ -3826,28 +3846,28 @@
         <v>79</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>533</v>
+        <v>107</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>31</v>
@@ -3856,28 +3876,28 @@
         <v>79</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>128</v>
+        <v>533</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>31</v>
@@ -3886,28 +3906,28 @@
         <v>79</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>31</v>
@@ -3916,28 +3936,28 @@
         <v>79</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>493</v>
+        <v>10</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>31</v>
@@ -3945,29 +3965,29 @@
       <c r="E61" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>247</v>
+      <c r="F61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>135</v>
+        <v>493</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>31</v>
@@ -3976,28 +3996,28 @@
         <v>79</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>5</v>
+        <v>217</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>5</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>31</v>
@@ -4005,29 +4025,29 @@
       <c r="E63" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>131</v>
+      <c r="F63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>31</v>
@@ -4036,28 +4056,28 @@
         <v>79</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>31</v>
@@ -4066,328 +4086,328 @@
         <v>79</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>166</v>
+      <c r="F66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>162</v>
+      <c r="F67" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>92</v>
+      <c r="F70" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="F71" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>492</v>
+        <v>204</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>219</v>
+        <v>492</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>491</v>
+        <v>219</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>245</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>223</v>
+        <v>491</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>92</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="3" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>31</v>
@@ -4396,13 +4416,13 @@
         <v>79</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>230</v>
+        <v>186</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>18</v>
@@ -4414,100 +4434,100 @@
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>249</v>
+        <v>127</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>126</v>
+        <v>250</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="3" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>32</v>
@@ -4515,62 +4535,62 @@
       <c r="E80" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>125</v>
+      <c r="F80" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="3" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>374</v>
+        <v>232</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>378</v>
+      <c r="F81" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>375</v>
+        <v>279</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>376</v>
+        <v>276</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>377</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>79</v>
@@ -4579,25 +4599,25 @@
         <v>378</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>5</v>
+        <v>375</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>5</v>
+      <c r="J82" s="3" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>32</v>
@@ -4605,59 +4625,59 @@
       <c r="E83" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>14</v>
+      <c r="F83" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>150</v>
+      <c r="J83" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="3" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>164</v>
+      <c r="F84" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>393</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>391</v>
+        <v>5</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="3" t="s">
-        <v>426</v>
+        <v>397</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>425</v>
+        <v>390</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>31</v>
@@ -4666,28 +4686,28 @@
         <v>79</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>428</v>
+        <v>164</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>391</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J85" s="4" t="s">
+      <c r="J85" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>31</v>
@@ -4696,28 +4716,28 @@
         <v>79</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>26</v>
+        <v>428</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>424</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>92</v>
+      <c r="J86" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>31</v>
@@ -4726,28 +4746,28 @@
         <v>79</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>247</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>31</v>
@@ -4756,10 +4776,10 @@
         <v>79</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>13</v>
+        <v>438</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>123</v>
@@ -4768,240 +4788,240 @@
         <v>18</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>25</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>414</v>
+        <v>13</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>98</v>
+        <v>414</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>490</v>
+        <v>411</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="H92" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>463</v>
+        <v>116</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>464</v>
+        <v>5</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>446</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="3" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>71</v>
+        <v>461</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F94" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A95" s="1"/>
+      <c r="B95" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G95" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J94" s="3" t="s">
+      <c r="I95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="12"/>
-      <c r="E95" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-    </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="1"/>
-      <c r="B96" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A96" s="12"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="12"/>
       <c r="E96" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J96" s="3">
-        <v>75</v>
-      </c>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>495</v>
+        <v>111</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>31</v>
@@ -5010,28 +5030,28 @@
         <v>80</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J97" s="3" t="s">
-        <v>92</v>
+      <c r="J97" s="3">
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>75</v>
+        <v>495</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>31</v>
@@ -5040,28 +5060,28 @@
         <v>80</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>139</v>
+        <v>84</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>31</v>
@@ -5070,43 +5090,43 @@
         <v>80</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>18</v>
@@ -5118,10 +5138,10 @@
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>158</v>
@@ -5130,28 +5150,28 @@
         <v>80</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>158</v>
@@ -5160,43 +5180,43 @@
         <v>80</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>177</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="3" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="E103" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>213</v>
+        <v>177</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>18</v>
@@ -5208,40 +5228,40 @@
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>9</v>
+        <v>214</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>216</v>
+        <v>22</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>158</v>
@@ -5250,28 +5270,28 @@
         <v>80</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>212</v>
+        <v>9</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>213</v>
+        <v>27</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
-      <c r="B106" s="19" t="s">
-        <v>239</v>
+      <c r="B106" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>158</v>
@@ -5285,8 +5305,8 @@
       <c r="G106" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H106" s="3" t="s">
-        <v>162</v>
+      <c r="H106" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>18</v>
@@ -5297,41 +5317,41 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
-      <c r="B107" s="3" t="s">
-        <v>258</v>
+      <c r="B107" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>32</v>
@@ -5340,7 +5360,7 @@
         <v>80</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>13</v>
@@ -5358,148 +5378,148 @@
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>264</v>
+        <v>74</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="3" t="s">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>364</v>
+        <v>264</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>367</v>
+        <v>140</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>372</v>
+        <v>31</v>
       </c>
       <c r="E111" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>371</v>
+        <v>214</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="3" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>93</v>
+        <v>372</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>105</v>
+        <v>371</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>418</v>
+        <v>105</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>13</v>
+        <v>414</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>139</v>
+        <v>413</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="J113" s="3" t="s">
         <v>92</v>
@@ -5508,10 +5528,10 @@
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="3" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>31</v>
@@ -5520,40 +5540,56 @@
         <v>80</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>7</v>
+        <v>418</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
+      <c r="B115" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>486</v>
+        <v>45</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -5567,7 +5603,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>46</v>
+        <v>486</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -5581,7 +5617,7 @@
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -5595,7 +5631,7 @@
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -5609,7 +5645,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -5623,7 +5659,7 @@
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>494</v>
+        <v>49</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -5634,56 +5670,40 @@
       <c r="J121" s="1"/>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A122" s="15"/>
-      <c r="B122" s="15"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="15"/>
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A123" s="1"/>
-      <c r="B123" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A123" s="15"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="15"/>
       <c r="E123" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="F123" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>90</v>
-      </c>
+      <c r="F123" s="15"/>
+      <c r="G123" s="15"/>
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="15"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="3" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>31</v>
@@ -5691,29 +5711,29 @@
       <c r="E124" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="F124" s="3" t="s">
-        <v>199</v>
+      <c r="F124" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>423</v>
+        <v>22</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>384</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="3" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>31</v>
@@ -5722,28 +5742,28 @@
         <v>81</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>22</v>
+        <v>423</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>240</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="3" t="s">
-        <v>383</v>
+        <v>225</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>382</v>
+        <v>224</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>31</v>
@@ -5752,28 +5772,28 @@
         <v>81</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>385</v>
+        <v>26</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>386</v>
+        <v>22</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>31</v>
@@ -5782,13 +5802,13 @@
         <v>81</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>401</v>
+        <v>5</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>384</v>
@@ -5800,25 +5820,25 @@
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="E128" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>116</v>
+        <v>400</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>384</v>
@@ -5830,40 +5850,40 @@
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="3" t="s">
-        <v>499</v>
+        <v>403</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>500</v>
+        <v>407</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="E129" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>501</v>
+        <v>116</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>502</v>
+        <v>406</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>384</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>504</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="3" t="s">
-        <v>420</v>
+        <v>499</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>419</v>
+        <v>500</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>31</v>
@@ -5872,40 +5892,56 @@
         <v>81</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>418</v>
+        <v>501</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>421</v>
+        <v>502</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>384</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="B131" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -5919,7 +5955,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -5933,7 +5969,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -5947,7 +5983,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -5961,7 +5997,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -5975,7 +6011,7 @@
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -5989,7 +6025,7 @@
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -6003,7 +6039,7 @@
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -6013,24 +6049,26 @@
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B142" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="17"/>
-      <c r="G142" s="17"/>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D143" s="17"/>
       <c r="E143" s="17"/>
@@ -6039,786 +6077,801 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D144" s="17"/>
       <c r="E144" s="17"/>
       <c r="F144" s="17"/>
       <c r="G144" s="17"/>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B145" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D145" s="17"/>
+      <c r="E145" s="17"/>
+      <c r="F145" s="17"/>
+      <c r="G145" s="17"/>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B146" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E145" s="17"/>
-      <c r="F145" s="18"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B146" s="3" t="s">
+      <c r="E146" s="17"/>
+      <c r="F146" s="18"/>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B147" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C147" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E146" s="17"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B147" s="3" t="s">
+      <c r="E147" s="17"/>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B148" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C148" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B148" s="3" t="s">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B149" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C149" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="3" t="s">
+    <row r="150" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B150" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C150" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B150" s="3" t="s">
+    <row r="151" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B151" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C151" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B151" s="3" t="s">
+    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B152" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C152" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="3" t="s">
+    <row r="153" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B153" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C153" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B153" s="3" t="s">
+    <row r="154" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B154" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C154" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B154" s="3" t="s">
+    <row r="155" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B155" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="C155" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B155" s="3" t="s">
+    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B156" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C156" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B156" s="3" t="s">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B157" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C157" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B157" s="3" t="s">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B158" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C158" s="3" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B158" s="3" t="s">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B159" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C159" s="3" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B159" s="3" t="s">
+    <row r="160" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B160" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C160" s="3" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B160" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B161" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B162" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>493</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B163" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>135</v>
+        <v>493</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B167" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B168" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B169" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B170" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B171" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B172" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B173" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B174" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B178" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B179" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B180" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B181" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B182" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B183" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>492</v>
+        <v>204</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B184" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>211</v>
+        <v>492</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B185" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>491</v>
+        <v>219</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>223</v>
+        <v>491</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B189" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B190" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B191" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B192" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B193" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>163</v>
+        <v>233</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B194" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B195" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B196" s="3" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>73</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B200" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>264</v>
+        <v>74</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B201" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B202" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B203" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B204" s="3" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>365</v>
+        <v>232</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B205" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B206" s="3" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B207" s="3" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B211" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B212" s="3" t="s">
-        <v>398</v>
+        <v>339</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B213" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B214" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B215" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B216" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B217" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B218" s="3" t="s">
-        <v>340</v>
+        <v>426</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B221" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B222" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B223" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B224" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B225" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>490</v>
+        <v>444</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B226" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B227" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B228" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B229" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B233" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B234" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B235" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>71</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B236" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>488</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B237" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B238" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B239" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B240" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B242" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C241" s="3" t="s">
+      <c r="C242" s="3" t="s">
         <v>419</v>
       </c>
     </row>
